--- a/artfynd/A 433-2026 artfynd.xlsx
+++ b/artfynd/A 433-2026 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>131110416</v>
       </c>
       <c r="B4" t="n">
-        <v>92251</v>
+        <v>92252</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 433-2026 artfynd.xlsx
+++ b/artfynd/A 433-2026 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>131110416</v>
       </c>
       <c r="B4" t="n">
-        <v>92252</v>
+        <v>92254</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 433-2026 artfynd.xlsx
+++ b/artfynd/A 433-2026 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>131110416</v>
       </c>
       <c r="B4" t="n">
-        <v>92254</v>
+        <v>92255</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 433-2026 artfynd.xlsx
+++ b/artfynd/A 433-2026 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>131110416</v>
       </c>
       <c r="B4" t="n">
-        <v>92255</v>
+        <v>92256</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 433-2026 artfynd.xlsx
+++ b/artfynd/A 433-2026 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>131110416</v>
       </c>
       <c r="B4" t="n">
-        <v>92256</v>
+        <v>92259</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 433-2026 artfynd.xlsx
+++ b/artfynd/A 433-2026 artfynd.xlsx
@@ -900,7 +900,7 @@
         <v>131110416</v>
       </c>
       <c r="B4" t="n">
-        <v>92259</v>
+        <v>92260</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
